--- a/Assets/Resources/DataFiles/CharData/ClassData/1. ExcelFile/FighterStatData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ClassData/1. ExcelFile/FighterStatData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Project2\Assets\Resources\DataFiles\CharData\ClassData\1. ExcelFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E2AF47-40F7-4817-981F-7FA3A6232CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CAAAE8-BE9E-4ACC-9BB8-438484798B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2265" yWindow="660" windowWidth="24450" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -550,7 +550,7 @@
         <v>600</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -565,7 +565,7 @@
         <v>10</v>
       </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="I3">
         <v>1.1000000000000001</v>
@@ -594,7 +594,7 @@
         <v>672</v>
       </c>
       <c r="C4">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="D4">
         <v>112</v>
@@ -609,7 +609,7 @@
         <v>11</v>
       </c>
       <c r="H4">
-        <v>3.22</v>
+        <v>5.08</v>
       </c>
       <c r="I4">
         <v>1.1200000000000001</v>
@@ -638,7 +638,7 @@
         <v>750</v>
       </c>
       <c r="C5">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="D5">
         <v>125</v>
@@ -653,7 +653,7 @@
         <v>12</v>
       </c>
       <c r="H5">
-        <v>3.24</v>
+        <v>5.14</v>
       </c>
       <c r="I5">
         <v>1.1399999999999999</v>
@@ -682,7 +682,7 @@
         <v>840</v>
       </c>
       <c r="C6">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="D6">
         <v>140</v>
@@ -697,7 +697,7 @@
         <v>13</v>
       </c>
       <c r="H6">
-        <v>3.26</v>
+        <v>5.2</v>
       </c>
       <c r="I6">
         <v>1.1599999999999999</v>
@@ -726,7 +726,7 @@
         <v>936</v>
       </c>
       <c r="C7">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="D7">
         <v>156</v>
@@ -741,7 +741,7 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>3.28</v>
+        <v>5.26</v>
       </c>
       <c r="I7">
         <v>1.18</v>
@@ -770,7 +770,7 @@
         <v>1044</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>235</v>
       </c>
       <c r="D8">
         <v>174</v>
@@ -785,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="H8">
-        <v>3.3</v>
+        <v>5.32</v>
       </c>
       <c r="I8">
         <v>1.2</v>
@@ -814,7 +814,7 @@
         <v>1170</v>
       </c>
       <c r="C9">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="D9">
         <v>195</v>
@@ -829,7 +829,7 @@
         <v>16</v>
       </c>
       <c r="H9">
-        <v>3.32</v>
+        <v>5.38</v>
       </c>
       <c r="I9">
         <v>1.22</v>
@@ -858,7 +858,7 @@
         <v>1308</v>
       </c>
       <c r="C10">
-        <v>65</v>
+        <v>265</v>
       </c>
       <c r="D10">
         <v>218</v>
@@ -873,7 +873,7 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>3.34</v>
+        <v>5.44</v>
       </c>
       <c r="I10">
         <v>1.24</v>
@@ -902,7 +902,7 @@
         <v>1458</v>
       </c>
       <c r="C11">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="D11">
         <v>243</v>
@@ -917,7 +917,7 @@
         <v>18</v>
       </c>
       <c r="H11">
-        <v>3.36</v>
+        <v>5.5</v>
       </c>
       <c r="I11">
         <v>1.26</v>
@@ -946,7 +946,7 @@
         <v>1626</v>
       </c>
       <c r="C12">
-        <v>70</v>
+        <v>295</v>
       </c>
       <c r="D12">
         <v>271</v>
@@ -961,7 +961,7 @@
         <v>19</v>
       </c>
       <c r="H12">
-        <v>3.38</v>
+        <v>5.56</v>
       </c>
       <c r="I12">
         <v>1.28</v>
@@ -990,7 +990,7 @@
         <v>1818</v>
       </c>
       <c r="C13">
-        <v>75</v>
+        <v>310</v>
       </c>
       <c r="D13">
         <v>303</v>
@@ -1005,7 +1005,7 @@
         <v>20</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>5.62</v>
       </c>
       <c r="I13">
         <v>1.3</v>
@@ -1034,7 +1034,7 @@
         <v>2034</v>
       </c>
       <c r="C14">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="D14">
         <v>339</v>
@@ -1049,7 +1049,7 @@
         <v>21</v>
       </c>
       <c r="H14">
-        <v>3.42</v>
+        <v>5.6800000000000104</v>
       </c>
       <c r="I14">
         <v>1.32</v>
@@ -1078,7 +1078,7 @@
         <v>2274</v>
       </c>
       <c r="C15">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="D15">
         <v>379</v>
@@ -1093,7 +1093,7 @@
         <v>22</v>
       </c>
       <c r="H15">
-        <v>3.44</v>
+        <v>5.74000000000001</v>
       </c>
       <c r="I15">
         <v>1.34</v>
@@ -1122,7 +1122,7 @@
         <v>2538</v>
       </c>
       <c r="C16">
-        <v>80</v>
+        <v>355</v>
       </c>
       <c r="D16">
         <v>423</v>
@@ -1137,7 +1137,7 @@
         <v>23</v>
       </c>
       <c r="H16">
-        <v>3.46</v>
+        <v>5.8000000000000096</v>
       </c>
       <c r="I16">
         <v>1.36</v>
@@ -1166,7 +1166,7 @@
         <v>2838</v>
       </c>
       <c r="C17">
-        <v>85</v>
+        <v>370</v>
       </c>
       <c r="D17">
         <v>473</v>
@@ -1181,7 +1181,7 @@
         <v>24</v>
       </c>
       <c r="H17">
-        <v>3.48</v>
+        <v>5.8600000000000101</v>
       </c>
       <c r="I17">
         <v>1.38</v>
@@ -1210,7 +1210,7 @@
         <v>3174</v>
       </c>
       <c r="C18">
-        <v>85</v>
+        <v>385</v>
       </c>
       <c r="D18">
         <v>529</v>
@@ -1225,7 +1225,7 @@
         <v>25</v>
       </c>
       <c r="H18">
-        <v>3.5</v>
+        <v>5.9200000000000097</v>
       </c>
       <c r="I18">
         <v>1.4</v>
@@ -1254,7 +1254,7 @@
         <v>3546</v>
       </c>
       <c r="C19">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="D19">
         <v>591</v>
@@ -1269,7 +1269,7 @@
         <v>26</v>
       </c>
       <c r="H19">
-        <v>3.52</v>
+        <v>5.9800000000000102</v>
       </c>
       <c r="I19">
         <v>1.42</v>
@@ -1298,7 +1298,7 @@
         <v>3960</v>
       </c>
       <c r="C20">
-        <v>90</v>
+        <v>415</v>
       </c>
       <c r="D20">
         <v>660</v>
@@ -1313,7 +1313,7 @@
         <v>27</v>
       </c>
       <c r="H20">
-        <v>3.54</v>
+        <v>6.0400000000000098</v>
       </c>
       <c r="I20">
         <v>1.44</v>
@@ -1342,7 +1342,7 @@
         <v>4428</v>
       </c>
       <c r="C21">
-        <v>95</v>
+        <v>430</v>
       </c>
       <c r="D21">
         <v>738</v>
@@ -1357,7 +1357,7 @@
         <v>28</v>
       </c>
       <c r="H21">
-        <v>3.56</v>
+        <v>6.1000000000000103</v>
       </c>
       <c r="I21">
         <v>1.46</v>
@@ -1386,7 +1386,7 @@
         <v>4944</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>445</v>
       </c>
       <c r="D22">
         <v>824</v>
@@ -1401,7 +1401,7 @@
         <v>29</v>
       </c>
       <c r="H22">
-        <v>3.58</v>
+        <v>6.1600000000000099</v>
       </c>
       <c r="I22">
         <v>1.48</v>

--- a/Assets/Resources/DataFiles/CharData/ClassData/1. ExcelFile/FighterStatData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ClassData/1. ExcelFile/FighterStatData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\CharData\ClassData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CAAAE8-BE9E-4ACC-9BB8-438484798B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAE728A-0066-4A07-A155-9EC0F56B6AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="660" windowWidth="24450" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -436,25 +436,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.125" style="1"/>
+    <col min="3" max="3" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" style="1"/>
     <col min="11" max="11" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,21 +542,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="C3">
         <v>160</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -586,21 +586,21 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>672</v>
+        <v>270</v>
       </c>
       <c r="C4">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D4">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -630,21 +630,21 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>750</v>
+        <v>290</v>
       </c>
       <c r="C5">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D5">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -674,21 +674,21 @@
         <v>499</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>840</v>
+        <v>310</v>
       </c>
       <c r="C6">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="D6">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -718,21 +718,21 @@
         <v>757</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>936</v>
+        <v>330</v>
       </c>
       <c r="C7">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="D7">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="E7">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -762,21 +762,21 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1044</v>
+        <v>350</v>
       </c>
       <c r="C8">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="D8">
-        <v>174</v>
+        <v>85</v>
       </c>
       <c r="E8">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -806,21 +806,21 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1170</v>
+        <v>370</v>
       </c>
       <c r="C9">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="D9">
-        <v>195</v>
+        <v>89</v>
       </c>
       <c r="E9">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F9">
         <v>11</v>
@@ -850,21 +850,21 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1308</v>
+        <v>390</v>
       </c>
       <c r="C10">
-        <v>265</v>
+        <v>209</v>
       </c>
       <c r="D10">
-        <v>218</v>
+        <v>93</v>
       </c>
       <c r="E10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F10">
         <v>12</v>
@@ -894,18 +894,18 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1458</v>
+        <v>410</v>
       </c>
       <c r="C11">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="D11">
-        <v>243</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>75</v>
@@ -938,21 +938,21 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1626</v>
+        <v>430</v>
       </c>
       <c r="C12">
-        <v>295</v>
+        <v>223</v>
       </c>
       <c r="D12">
-        <v>271</v>
+        <v>101</v>
       </c>
       <c r="E12">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F12">
         <v>14</v>
@@ -982,21 +982,21 @@
         <v>2828</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1818</v>
+        <v>450</v>
       </c>
       <c r="C13">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="D13">
-        <v>303</v>
+        <v>105</v>
       </c>
       <c r="E13">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="F13">
         <v>15</v>
@@ -1026,21 +1026,21 @@
         <v>3243</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2034</v>
+        <v>470</v>
       </c>
       <c r="C14">
-        <v>325</v>
+        <v>237</v>
       </c>
       <c r="D14">
-        <v>339</v>
+        <v>109</v>
       </c>
       <c r="E14">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="F14">
         <v>16</v>
@@ -1070,21 +1070,21 @@
         <v>3674</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2274</v>
+        <v>490</v>
       </c>
       <c r="C15">
-        <v>340</v>
+        <v>244</v>
       </c>
       <c r="D15">
-        <v>379</v>
+        <v>113</v>
       </c>
       <c r="E15">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="F15">
         <v>17</v>
@@ -1114,21 +1114,21 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>2538</v>
+        <v>510</v>
       </c>
       <c r="C16">
-        <v>355</v>
+        <v>251</v>
       </c>
       <c r="D16">
-        <v>423</v>
+        <v>117</v>
       </c>
       <c r="E16">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>18</v>
@@ -1158,21 +1158,21 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17">
-        <v>2838</v>
+        <v>530</v>
       </c>
       <c r="C17">
-        <v>370</v>
+        <v>258</v>
       </c>
       <c r="D17">
-        <v>473</v>
+        <v>121</v>
       </c>
       <c r="E17">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="F17">
         <v>19</v>
@@ -1202,21 +1202,21 @@
         <v>5057</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18">
-        <v>3174</v>
+        <v>550</v>
       </c>
       <c r="C18">
-        <v>385</v>
+        <v>265</v>
       </c>
       <c r="D18">
-        <v>529</v>
+        <v>125</v>
       </c>
       <c r="E18">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1246,21 +1246,21 @@
         <v>5545</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19">
-        <v>3546</v>
+        <v>570</v>
       </c>
       <c r="C19">
-        <v>400</v>
+        <v>272</v>
       </c>
       <c r="D19">
-        <v>591</v>
+        <v>129</v>
       </c>
       <c r="E19">
-        <v>212</v>
+        <v>115</v>
       </c>
       <c r="F19">
         <v>21</v>
@@ -1290,21 +1290,21 @@
         <v>6045</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20">
-        <v>3960</v>
+        <v>590</v>
       </c>
       <c r="C20">
-        <v>415</v>
+        <v>279</v>
       </c>
       <c r="D20">
-        <v>660</v>
+        <v>133</v>
       </c>
       <c r="E20">
-        <v>236</v>
+        <v>120</v>
       </c>
       <c r="F20">
         <v>22</v>
@@ -1334,21 +1334,21 @@
         <v>6558</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>4428</v>
+        <v>610</v>
       </c>
       <c r="C21">
-        <v>430</v>
+        <v>286</v>
       </c>
       <c r="D21">
-        <v>738</v>
+        <v>137</v>
       </c>
       <c r="E21">
-        <v>261</v>
+        <v>125</v>
       </c>
       <c r="F21">
         <v>23</v>
@@ -1378,21 +1378,21 @@
         <v>7082</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22">
-        <v>4944</v>
+        <v>630</v>
       </c>
       <c r="C22">
-        <v>445</v>
+        <v>293</v>
       </c>
       <c r="D22">
-        <v>824</v>
+        <v>141</v>
       </c>
       <c r="E22">
-        <v>287</v>
+        <v>130</v>
       </c>
       <c r="F22">
         <v>24</v>
